--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_REAL CANOE N.C..xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_REAL CANOE N.C..xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D. MANZANERO CAMACHO</t>
+          <t>L. GARCIA LARRACHE SEGURA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>30.5302</v>
+        <v>21.8472</v>
       </c>
       <c r="E2" t="n">
-        <v>12.6271</v>
+        <v>23.238</v>
       </c>
       <c r="F2" t="n">
-        <v>17.9036</v>
+        <v>-1.390799999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>-4.618</v>
+        <v>48.9852</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7851999999999992</v>
+        <v>25.276</v>
       </c>
       <c r="I2" t="n">
-        <v>-5.4028</v>
+        <v>23.7087</v>
       </c>
       <c r="J2" t="n">
-        <v>23.6293</v>
+        <v>65.4093</v>
       </c>
       <c r="K2" t="n">
-        <v>23.0977</v>
+        <v>35.4597</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5317999999999996</v>
+        <v>29.9492</v>
       </c>
       <c r="M2" t="n">
-        <v>-28.247</v>
+        <v>-16.4242</v>
       </c>
       <c r="N2" t="n">
-        <v>-22.3127</v>
+        <v>-10.1837</v>
       </c>
       <c r="O2" t="n">
-        <v>-5.9343</v>
+        <v>-6.2406</v>
       </c>
       <c r="P2" t="n">
-        <v>5.238599999999999</v>
+        <v>-23.866</v>
       </c>
       <c r="Q2" t="n">
-        <v>-38.2245</v>
+        <v>-73.3442</v>
       </c>
       <c r="R2" t="n">
-        <v>43.4635</v>
+        <v>49.4783</v>
       </c>
       <c r="S2" t="n">
-        <v>17.8001</v>
+        <v>-4.8255</v>
       </c>
       <c r="T2" t="n">
-        <v>7.041300000000001</v>
+        <v>-2.2402</v>
       </c>
       <c r="U2" t="n">
-        <v>10.7587</v>
+        <v>-2.5857</v>
       </c>
       <c r="V2" t="n">
-        <v>12.1091</v>
+        <v>1.553799999999999</v>
       </c>
       <c r="W2" t="n">
-        <v>20.1801</v>
+        <v>33.4133</v>
       </c>
       <c r="X2" t="n">
-        <v>-8.071300000000001</v>
+        <v>-31.8594</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. LAPASTORA ARACIL</t>
+          <t>D. MANZANERO CAMACHO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D3" t="n">
-        <v>26.9021</v>
+        <v>18.8121</v>
       </c>
       <c r="E3" t="n">
-        <v>34.5923</v>
+        <v>7.927500000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>-7.6904</v>
+        <v>10.8849</v>
       </c>
       <c r="G3" t="n">
-        <v>-11.6382</v>
+        <v>-4.618</v>
       </c>
       <c r="H3" t="n">
-        <v>-5.870099999999999</v>
+        <v>0.7851999999999992</v>
       </c>
       <c r="I3" t="n">
-        <v>-5.767799999999999</v>
+        <v>-5.4028</v>
       </c>
       <c r="J3" t="n">
-        <v>17.2405</v>
+        <v>23.6293</v>
       </c>
       <c r="K3" t="n">
-        <v>14.0928</v>
+        <v>23.0977</v>
       </c>
       <c r="L3" t="n">
-        <v>3.1473</v>
+        <v>0.5317999999999996</v>
       </c>
       <c r="M3" t="n">
-        <v>-28.8782</v>
+        <v>-28.247</v>
       </c>
       <c r="N3" t="n">
-        <v>-19.9631</v>
+        <v>-22.3127</v>
       </c>
       <c r="O3" t="n">
-        <v>-8.9156</v>
+        <v>-5.9343</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.3881999999999998</v>
+        <v>5.238599999999999</v>
       </c>
       <c r="Q3" t="n">
-        <v>-45.9858</v>
+        <v>-38.2245</v>
       </c>
       <c r="R3" t="n">
-        <v>45.5979</v>
+        <v>43.4635</v>
       </c>
       <c r="S3" t="n">
-        <v>12.8804</v>
+        <v>6.0822</v>
       </c>
       <c r="T3" t="n">
-        <v>17.6426</v>
+        <v>2.3415</v>
       </c>
       <c r="U3" t="n">
-        <v>-4.762</v>
+        <v>3.7405</v>
       </c>
       <c r="V3" t="n">
-        <v>26.0475</v>
+        <v>12.1091</v>
       </c>
       <c r="W3" t="n">
-        <v>45.6951</v>
+        <v>20.1801</v>
       </c>
       <c r="X3" t="n">
-        <v>-19.6475</v>
+        <v>-8.071300000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. HERMOSO ALCUBILLA</t>
+          <t>M. KREISLER LORENTE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D4" t="n">
-        <v>25.4011</v>
+        <v>18.0666</v>
       </c>
       <c r="E4" t="n">
-        <v>15.0491</v>
+        <v>-1.452599999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>10.3521</v>
+        <v>19.5193</v>
       </c>
       <c r="G4" t="n">
-        <v>-4.745900000000002</v>
+        <v>5.177700000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3838999999999997</v>
+        <v>14.0082</v>
       </c>
       <c r="I4" t="n">
-        <v>-5.1298</v>
+        <v>-8.830400000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>13.4501</v>
+        <v>20.1688</v>
       </c>
       <c r="K4" t="n">
-        <v>9.203099999999999</v>
+        <v>22.6032</v>
       </c>
       <c r="L4" t="n">
-        <v>4.2469</v>
+        <v>-2.4342</v>
       </c>
       <c r="M4" t="n">
-        <v>-18.196</v>
+        <v>-14.9913</v>
       </c>
       <c r="N4" t="n">
-        <v>-8.8195</v>
+        <v>-8.5951</v>
       </c>
       <c r="O4" t="n">
-        <v>-9.3767</v>
+        <v>-6.3959</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1940999999999999</v>
+        <v>9.8955</v>
       </c>
       <c r="Q4" t="n">
-        <v>-38.2245</v>
+        <v>-31.8217</v>
       </c>
       <c r="R4" t="n">
-        <v>38.4186</v>
+        <v>41.7171</v>
       </c>
       <c r="S4" t="n">
-        <v>10.9193</v>
+        <v>-1.4086</v>
       </c>
       <c r="T4" t="n">
-        <v>10.9764</v>
+        <v>0.3657000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.05700000000000027</v>
+        <v>-1.774</v>
       </c>
       <c r="V4" t="n">
-        <v>19.0341</v>
+        <v>4.4017</v>
       </c>
       <c r="W4" t="n">
-        <v>28.8477</v>
+        <v>9.834300000000001</v>
       </c>
       <c r="X4" t="n">
-        <v>-9.813500000000001</v>
+        <v>-5.4326</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. KREISLER LORENTE</t>
+          <t>J. LAPASTORA ARACIL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>26</v>
       </c>
       <c r="D5" t="n">
-        <v>13.2322</v>
+        <v>18.0078</v>
       </c>
       <c r="E5" t="n">
-        <v>-3.7394</v>
+        <v>25.2487</v>
       </c>
       <c r="F5" t="n">
-        <v>16.9716</v>
+        <v>-7.2411</v>
       </c>
       <c r="G5" t="n">
-        <v>5.177700000000001</v>
+        <v>-11.6382</v>
       </c>
       <c r="H5" t="n">
-        <v>14.0082</v>
+        <v>-5.870099999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-8.830400000000001</v>
+        <v>-5.767799999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>20.1688</v>
+        <v>17.2405</v>
       </c>
       <c r="K5" t="n">
-        <v>22.6032</v>
+        <v>14.0928</v>
       </c>
       <c r="L5" t="n">
-        <v>-2.4342</v>
+        <v>3.1473</v>
       </c>
       <c r="M5" t="n">
-        <v>-14.9913</v>
+        <v>-28.8782</v>
       </c>
       <c r="N5" t="n">
-        <v>-8.5951</v>
+        <v>-19.9631</v>
       </c>
       <c r="O5" t="n">
-        <v>-6.3959</v>
+        <v>-8.9156</v>
       </c>
       <c r="P5" t="n">
-        <v>9.8955</v>
+        <v>-0.3881999999999998</v>
       </c>
       <c r="Q5" t="n">
-        <v>-31.8217</v>
+        <v>-45.9858</v>
       </c>
       <c r="R5" t="n">
-        <v>41.7171</v>
+        <v>45.5979</v>
       </c>
       <c r="S5" t="n">
-        <v>-6.242999999999999</v>
+        <v>3.986</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.9206</v>
+        <v>8.2986</v>
       </c>
       <c r="U5" t="n">
-        <v>-4.3223</v>
+        <v>-4.3131</v>
       </c>
       <c r="V5" t="n">
-        <v>4.4017</v>
+        <v>26.0475</v>
       </c>
       <c r="W5" t="n">
-        <v>9.834300000000001</v>
+        <v>45.6951</v>
       </c>
       <c r="X5" t="n">
-        <v>-5.4326</v>
+        <v>-19.6475</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. GARCIA LARRACHE SEGURA</t>
+          <t>M. HERMOSO ALCUBILLA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,70 +874,70 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D6" t="n">
-        <v>10.473</v>
+        <v>15.759</v>
       </c>
       <c r="E6" t="n">
-        <v>14.7063</v>
+        <v>6.287499999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>-4.2329</v>
+        <v>9.4716</v>
       </c>
       <c r="G6" t="n">
-        <v>48.9852</v>
+        <v>-4.745900000000002</v>
       </c>
       <c r="H6" t="n">
-        <v>25.276</v>
+        <v>0.3838999999999997</v>
       </c>
       <c r="I6" t="n">
-        <v>23.7087</v>
+        <v>-5.1298</v>
       </c>
       <c r="J6" t="n">
-        <v>65.4093</v>
+        <v>13.4501</v>
       </c>
       <c r="K6" t="n">
-        <v>35.4597</v>
+        <v>9.203099999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>29.9492</v>
+        <v>4.2469</v>
       </c>
       <c r="M6" t="n">
-        <v>-16.4242</v>
+        <v>-18.196</v>
       </c>
       <c r="N6" t="n">
-        <v>-10.1837</v>
+        <v>-8.8195</v>
       </c>
       <c r="O6" t="n">
-        <v>-6.2406</v>
+        <v>-9.3767</v>
       </c>
       <c r="P6" t="n">
-        <v>-23.866</v>
+        <v>0.1940999999999999</v>
       </c>
       <c r="Q6" t="n">
-        <v>-73.3442</v>
+        <v>-38.2245</v>
       </c>
       <c r="R6" t="n">
-        <v>49.4783</v>
+        <v>38.4186</v>
       </c>
       <c r="S6" t="n">
-        <v>-16.2</v>
+        <v>1.277</v>
       </c>
       <c r="T6" t="n">
-        <v>-10.7723</v>
+        <v>2.2146</v>
       </c>
       <c r="U6" t="n">
-        <v>-5.4277</v>
+        <v>-0.9373</v>
       </c>
       <c r="V6" t="n">
-        <v>1.553799999999999</v>
+        <v>19.0341</v>
       </c>
       <c r="W6" t="n">
-        <v>33.4133</v>
+        <v>28.8477</v>
       </c>
       <c r="X6" t="n">
-        <v>-31.8594</v>
+        <v>-9.813500000000001</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>7.4541</v>
+        <v>7.3956</v>
       </c>
       <c r="E7" t="n">
-        <v>11.1666</v>
+        <v>10.8083</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.7126</v>
+        <v>-3.4128</v>
       </c>
       <c r="G7" t="n">
         <v>1.5874</v>
@@ -1000,13 +1000,13 @@
         <v>13.1941</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1872000000000001</v>
+        <v>-0.2456</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4843000000000002</v>
+        <v>0.1260000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6715</v>
+        <v>-0.3715000000000001</v>
       </c>
       <c r="V7" t="n">
         <v>1.9791</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. OLIVA SANCHEZ</t>
+          <t>E. PASCUAL COZAR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="D8" t="n">
-        <v>6.247199999999999</v>
+        <v>7.124299999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>4.4697</v>
+        <v>9.5548</v>
       </c>
       <c r="F8" t="n">
-        <v>1.777200000000001</v>
+        <v>-2.4308</v>
       </c>
       <c r="G8" t="n">
-        <v>1.911100000000001</v>
+        <v>9.410299999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3536000000000001</v>
+        <v>-2.026000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>2.2644</v>
+        <v>11.4363</v>
       </c>
       <c r="J8" t="n">
-        <v>10.6734</v>
+        <v>32.6569</v>
       </c>
       <c r="K8" t="n">
-        <v>5.6725</v>
+        <v>12.7166</v>
       </c>
       <c r="L8" t="n">
-        <v>5.0007</v>
+        <v>19.9402</v>
       </c>
       <c r="M8" t="n">
-        <v>-8.7623</v>
+        <v>-23.2464</v>
       </c>
       <c r="N8" t="n">
-        <v>-6.0259</v>
+        <v>-14.7427</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.7362</v>
+        <v>-8.503399999999999</v>
       </c>
       <c r="P8" t="n">
-        <v>1.9404</v>
+        <v>2.716200000000001</v>
       </c>
       <c r="Q8" t="n">
-        <v>-11.642</v>
+        <v>-29.1048</v>
       </c>
       <c r="R8" t="n">
-        <v>13.5824</v>
+        <v>31.8213</v>
       </c>
       <c r="S8" t="n">
-        <v>2.348</v>
+        <v>-5.5537</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1219</v>
+        <v>-4.2047</v>
       </c>
       <c r="U8" t="n">
-        <v>2.2262</v>
+        <v>-1.3493</v>
       </c>
       <c r="V8" t="n">
-        <v>0.04780000000000018</v>
+        <v>0.551</v>
       </c>
       <c r="W8" t="n">
-        <v>5.3164</v>
+        <v>10.2073</v>
       </c>
       <c r="X8" t="n">
-        <v>-5.2686</v>
+        <v>-9.6563</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. ALONSO GONZÁLEZ</t>
+          <t>J. OLIVA SANCHEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,70 +1108,70 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6358999999999997</v>
+        <v>5.1366</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2561</v>
+        <v>5.212499999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>1.6202</v>
+        <v>-0.07589999999999986</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.8854</v>
+        <v>1.911100000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4886</v>
+        <v>-0.3536000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.3741</v>
+        <v>2.2644</v>
       </c>
       <c r="J9" t="n">
-        <v>1.3365</v>
+        <v>10.6734</v>
       </c>
       <c r="K9" t="n">
-        <v>0.375</v>
+        <v>5.6725</v>
       </c>
       <c r="L9" t="n">
-        <v>0.9615999999999998</v>
+        <v>5.0007</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.222</v>
+        <v>-8.7623</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1137000000000001</v>
+        <v>-6.0259</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.3358</v>
+        <v>-2.7362</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.9701</v>
+        <v>1.9404</v>
       </c>
       <c r="Q9" t="n">
-        <v>-4.0747</v>
+        <v>-11.642</v>
       </c>
       <c r="R9" t="n">
-        <v>3.1046</v>
+        <v>13.5824</v>
       </c>
       <c r="S9" t="n">
-        <v>1.4361</v>
+        <v>1.2374</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.08189999999999995</v>
+        <v>0.8647</v>
       </c>
       <c r="U9" t="n">
-        <v>1.518</v>
+        <v>0.3726000000000003</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2161</v>
+        <v>0.04780000000000018</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5642</v>
+        <v>5.3164</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.7803</v>
+        <v>-5.2686</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>18</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.481499999999999</v>
+        <v>-0.3962000000000006</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9090999999999998</v>
+        <v>1.213999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.5725</v>
+        <v>-1.6104</v>
       </c>
       <c r="G10" t="n">
         <v>11.1537</v>
@@ -1234,13 +1234,13 @@
         <v>10.4778</v>
       </c>
       <c r="S10" t="n">
-        <v>-3.6623</v>
+        <v>0.4229000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.5684</v>
+        <v>0.5548</v>
       </c>
       <c r="U10" t="n">
-        <v>-2.0945</v>
+        <v>-0.1320999999999998</v>
       </c>
       <c r="V10" t="n">
         <v>-1.3011</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>E. PASCUAL COZAR</t>
+          <t>M. ALONSO GONZÁLEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,70 +1264,70 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.7541</v>
+        <v>-1.4815</v>
       </c>
       <c r="E11" t="n">
-        <v>0.05909999999999971</v>
+        <v>-2.4748</v>
       </c>
       <c r="F11" t="n">
-        <v>-6.8132</v>
+        <v>0.9932999999999996</v>
       </c>
       <c r="G11" t="n">
-        <v>9.410299999999999</v>
+        <v>-0.8854</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.026000000000001</v>
+        <v>0.4886</v>
       </c>
       <c r="I11" t="n">
-        <v>11.4363</v>
+        <v>-1.3741</v>
       </c>
       <c r="J11" t="n">
-        <v>32.6569</v>
+        <v>1.3365</v>
       </c>
       <c r="K11" t="n">
-        <v>12.7166</v>
+        <v>0.375</v>
       </c>
       <c r="L11" t="n">
-        <v>19.9402</v>
+        <v>0.9615999999999998</v>
       </c>
       <c r="M11" t="n">
-        <v>-23.2464</v>
+        <v>-2.222</v>
       </c>
       <c r="N11" t="n">
-        <v>-14.7427</v>
+        <v>0.1137000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>-8.503399999999999</v>
+        <v>-2.3358</v>
       </c>
       <c r="P11" t="n">
-        <v>2.716200000000001</v>
+        <v>-0.9701</v>
       </c>
       <c r="Q11" t="n">
-        <v>-29.1048</v>
+        <v>-4.0747</v>
       </c>
       <c r="R11" t="n">
-        <v>31.8213</v>
+        <v>3.1046</v>
       </c>
       <c r="S11" t="n">
-        <v>-19.4323</v>
+        <v>0.5905</v>
       </c>
       <c r="T11" t="n">
-        <v>-13.7008</v>
+        <v>-0.3007</v>
       </c>
       <c r="U11" t="n">
-        <v>-5.7316</v>
+        <v>0.8911</v>
       </c>
       <c r="V11" t="n">
-        <v>0.551</v>
+        <v>-0.2161</v>
       </c>
       <c r="W11" t="n">
-        <v>10.2073</v>
+        <v>0.5642</v>
       </c>
       <c r="X11" t="n">
-        <v>-9.6563</v>
+        <v>-0.7803</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>25</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.873100000000001</v>
+        <v>-14.3172</v>
       </c>
       <c r="E12" t="n">
-        <v>-21.708</v>
+        <v>-24.7452</v>
       </c>
       <c r="F12" t="n">
-        <v>12.8346</v>
+        <v>10.4281</v>
       </c>
       <c r="G12" t="n">
         <v>-8.047600000000001</v>
@@ -1390,13 +1390,13 @@
         <v>41.911</v>
       </c>
       <c r="S12" t="n">
-        <v>9.046099999999999</v>
+        <v>3.6015</v>
       </c>
       <c r="T12" t="n">
-        <v>3.8678</v>
+        <v>0.8303999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>5.1783</v>
+        <v>2.7718</v>
       </c>
       <c r="V12" t="n">
         <v>-19.3787</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>E. MARTINEZ ALVAREZ</t>
+          <t>N. LASUNCION MARIBLANCA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D13" t="n">
-        <v>-30.9759</v>
+        <v>-21.623</v>
       </c>
       <c r="E13" t="n">
-        <v>-30.9539</v>
+        <v>-4.017400000000002</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.0217000000000005</v>
+        <v>-17.6058</v>
       </c>
       <c r="G13" t="n">
-        <v>-11.6083</v>
+        <v>2.0128</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.9388</v>
+        <v>-11.1757</v>
       </c>
       <c r="I13" t="n">
-        <v>-9.6698</v>
+        <v>13.1888</v>
       </c>
       <c r="J13" t="n">
-        <v>2.4402</v>
+        <v>27.8772</v>
       </c>
       <c r="K13" t="n">
-        <v>8.383100000000001</v>
+        <v>3.8597</v>
       </c>
       <c r="L13" t="n">
-        <v>-5.9433</v>
+        <v>24.0172</v>
       </c>
       <c r="M13" t="n">
-        <v>-14.0484</v>
+        <v>-25.8645</v>
       </c>
       <c r="N13" t="n">
-        <v>-10.322</v>
+        <v>-15.0363</v>
       </c>
       <c r="O13" t="n">
-        <v>-3.7262</v>
+        <v>-10.8284</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.910299999999999</v>
+        <v>-13.1942</v>
       </c>
       <c r="Q13" t="n">
-        <v>-32.79179999999999</v>
+        <v>-43.4632</v>
       </c>
       <c r="R13" t="n">
-        <v>29.881</v>
+        <v>30.2691</v>
       </c>
       <c r="S13" t="n">
-        <v>-9.348000000000001</v>
+        <v>-4.1998</v>
       </c>
       <c r="T13" t="n">
-        <v>-6.3396</v>
+        <v>-2.7834</v>
       </c>
       <c r="U13" t="n">
-        <v>-3.0086</v>
+        <v>-1.4166</v>
       </c>
       <c r="V13" t="n">
-        <v>-7.1092</v>
+        <v>-6.241400000000001</v>
       </c>
       <c r="W13" t="n">
-        <v>5.7372</v>
+        <v>14.3519</v>
       </c>
       <c r="X13" t="n">
-        <v>-12.8462</v>
+        <v>-20.5938</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>N. LASUNCION MARIBLANCA</t>
+          <t>E. MARTINEZ ALVAREZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,70 +1498,70 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D14" t="n">
-        <v>-33.1328</v>
+        <v>-28.2161</v>
       </c>
       <c r="E14" t="n">
-        <v>-11.2481</v>
+        <v>-28.889</v>
       </c>
       <c r="F14" t="n">
-        <v>-21.8848</v>
+        <v>0.6724000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>2.0128</v>
+        <v>-11.6083</v>
       </c>
       <c r="H14" t="n">
-        <v>-11.1757</v>
+        <v>-1.9388</v>
       </c>
       <c r="I14" t="n">
-        <v>13.1888</v>
+        <v>-9.6698</v>
       </c>
       <c r="J14" t="n">
-        <v>27.8772</v>
+        <v>2.4402</v>
       </c>
       <c r="K14" t="n">
-        <v>3.8597</v>
+        <v>8.383100000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>24.0172</v>
+        <v>-5.9433</v>
       </c>
       <c r="M14" t="n">
-        <v>-25.8645</v>
+        <v>-14.0484</v>
       </c>
       <c r="N14" t="n">
-        <v>-15.0363</v>
+        <v>-10.322</v>
       </c>
       <c r="O14" t="n">
-        <v>-10.8284</v>
+        <v>-3.7262</v>
       </c>
       <c r="P14" t="n">
-        <v>-13.1942</v>
+        <v>-2.910299999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>-43.4632</v>
+        <v>-32.79179999999999</v>
       </c>
       <c r="R14" t="n">
-        <v>30.2691</v>
+        <v>29.881</v>
       </c>
       <c r="S14" t="n">
-        <v>-15.7095</v>
+        <v>-6.5883</v>
       </c>
       <c r="T14" t="n">
-        <v>-10.0142</v>
+        <v>-4.2746</v>
       </c>
       <c r="U14" t="n">
-        <v>-5.6956</v>
+        <v>-2.3138</v>
       </c>
       <c r="V14" t="n">
-        <v>-6.241400000000001</v>
+        <v>-7.1092</v>
       </c>
       <c r="W14" t="n">
-        <v>14.3519</v>
+        <v>5.7372</v>
       </c>
       <c r="X14" t="n">
-        <v>-20.5938</v>
+        <v>-12.8462</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>26</v>
       </c>
       <c r="D15" t="n">
-        <v>35.38659999999999</v>
+        <v>46.1152</v>
       </c>
       <c r="E15" t="n">
-        <v>21.8556</v>
+        <v>27.91230000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>13.53120000000001</v>
+        <v>18.202</v>
       </c>
       <c r="G15" t="n">
         <v>38.69479999999999</v>
@@ -1603,7 +1603,7 @@
         <v>155.4507</v>
       </c>
       <c r="L15" t="n">
-        <v>96.35510000000001</v>
+        <v>96.35510000000002</v>
       </c>
       <c r="M15" t="n">
         <v>-213.1118</v>
@@ -1618,19 +1618,19 @@
         <v>-18.4337</v>
       </c>
       <c r="Q15" t="n">
-        <v>-411.3504</v>
+        <v>-411.3503999999999</v>
       </c>
       <c r="R15" t="n">
         <v>392.9167</v>
       </c>
       <c r="S15" t="n">
-        <v>-16.3523</v>
+        <v>-5.624</v>
       </c>
       <c r="T15" t="n">
-        <v>-4.263500000000001</v>
+        <v>1.792700000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>-12.0896</v>
+        <v>-7.417399999999999</v>
       </c>
       <c r="V15" t="n">
         <v>31.47759999999999</v>
